--- a/版本更新记录.xlsx
+++ b/版本更新记录.xlsx
@@ -1,178 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="版本更新记录" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本更新记录" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
-  <si>
-    <t>FT课程开发 Skill — 版本更新记录</t>
-  </si>
-  <si>
-    <t>版本号</t>
-  </si>
-  <si>
-    <t>发布日期</t>
-  </si>
-  <si>
-    <t>更新类型</t>
-  </si>
-  <si>
-    <t>更新摘要</t>
-  </si>
-  <si>
-    <t>反向提示词条数</t>
-  </si>
-  <si>
-    <t>空白模板版本</t>
-  </si>
-  <si>
-    <t>GitHub Tag</t>
-  </si>
-  <si>
-    <t>v1.0</t>
-  </si>
-  <si>
-    <t>新建</t>
-  </si>
-  <si>
-    <t>初始版本：7步工作流（解析基础信息→教学目标→二级矩阵→KSA→三级矩阵→正文确认→组装docx）。FT方法论硬约束（1学时=1课点，毕业要求5+10，外显行为动词，★/☆标注规则）。</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>v2.0</t>
-  </si>
-  <si>
-    <t>增强</t>
-  </si>
-  <si>
-    <t>新增第6步"开课说明正文一次性确认"；课程要求7条模板固定文本；考核评价双表结构；反向提示词15条。首版《人工智能通识》开课说明生成。</t>
-  </si>
-  <si>
-    <t>15条</t>
-  </si>
-  <si>
-    <t>v3.0</t>
-  </si>
-  <si>
-    <t>重构</t>
-  </si>
-  <si>
-    <t>教学目标强制外显行为动词（禁止"完成xx"）；二级矩阵每格含完整★/☆+课点编号+名称；三级矩阵严格7列模板（课点|教学目标KSA|学法|教法|学习产出|周数|学时）；项目描述丰满段落；课程要求含7条固定文本；考核双表结构。</t>
-  </si>
-  <si>
-    <t>v4.0</t>
-  </si>
-  <si>
-    <t>新增</t>
-  </si>
-  <si>
-    <t>双模式选择：🅰 自主生成（全程无交互直接出docx）/ 🅱 人机协作（7步分步确认）。启动时提供选择。</t>
-  </si>
-  <si>
-    <t>v4</t>
-  </si>
-  <si>
-    <t>v5.0</t>
-  </si>
-  <si>
-    <t>修正</t>
-  </si>
-  <si>
-    <t>二级矩阵规则修正：同项目课点分散在不同教学目标下（非集中）；二级/三级矩阵表头教学目标列写完整全文（不可简写）；思政融入覆盖全部课点（两大段叙述+精简表格）；教学目标加整体介绍段落；去掉课程进度表，附件直接一级→二级→三级矩阵；反向提示词21条。</t>
-  </si>
-  <si>
-    <t>21条</t>
-  </si>
-  <si>
-    <t>v5</t>
-  </si>
-  <si>
-    <t>v6.0</t>
-  </si>
-  <si>
-    <t>KSA编号全局唯一连续（K1-K96, S1-S64），禁止跨课点重复；教学目标严格引用大纲原文只字不差，去掉[]；空白模板课程基本信息精简为13项（去课程代码/性质/类别/考核/先修/后续），每项单独一行；启动时必问周次；二级矩阵设计前确认项目关系（并列/递进/包含）；三级矩阵每项末行"学习产出及测量标准（以教学目标为单位考核）"；1学时=1课点修正（项目二8→12课点，项目三14→10课点）；反向提示词26条。</t>
-  </si>
-  <si>
-    <t>26条</t>
-  </si>
-  <si>
-    <t>v6</t>
-  </si>
-  <si>
-    <t>v7.0</t>
-  </si>
-  <si>
-    <t>课程实施绑定句式：当涉及教学组织形式/团队学习方式/课堂互动方法时，自然嵌入"工作坊式的教学组织形式，集体主义的团队学习方式，教学相长的212学习方法。"三句连写不可拆分改动。212释义：2分钟小组展示、1分钟学生点评、2分钟教师点评。不强制放段首。反向提示词27条。新增Git Tag + GitHub Release发布规范。</t>
-  </si>
-  <si>
-    <t>27条</t>
-  </si>
-  <si>
-    <t>v7</t>
-  </si>
-  <si>
-    <t>当前最新版本：v7.0 | 发布日期：2026-05-18 | 反向提示词：27条 | 空白模板：v7 | GitHub: https://github.com/mokch556-stack/ft-kecheng-kaifa</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
       <name val="黑体"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="黑体"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="楷体"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -196,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -219,45 +104,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -545,229 +544,371 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="65.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col width="10.7109375" customWidth="1" min="1" max="1"/>
+    <col width="14.7109375" customWidth="1" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" min="3" max="3"/>
+    <col width="65.7109375" customWidth="1" min="4" max="4"/>
+    <col width="16.7109375" customWidth="1" min="5" max="5"/>
+    <col width="14.7109375" customWidth="1" min="6" max="6"/>
+    <col width="16.7109375" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="22" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="72" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FT课程开发 Skill — 版本更新记录</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>发布日期</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>更新类型</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>更新摘要</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>反向提示词条数</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>空白模板版本</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>GitHub Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>46158</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="72" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>初始版本：7步工作流（解析基础信息→教学目标→二级矩阵→KSA→三级矩阵→正文确认→组装docx）。FT方法论硬约束（1学时=1课点，毕业要求5+10，外显行为动词，★/☆标注规则）。</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
         <v>46158</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="72" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>增强</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>新增第6步"开课说明正文一次性确认"；课程要求7条模板固定文本；考核评价双表结构；反向提示词15条。首版《人工智能通识》开课说明生成。</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15条</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>v3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>46159</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="72" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重构</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>教学目标强制外显行为动词（禁止"完成xx"）；二级矩阵每格含完整★/☆+课点编号+名称；三级矩阵严格7列模板（课点|教学目标KSA|学法|教法|学习产出|周数|学时）；项目描述丰满段落；课程要求含7条固定文本；考核双表结构。</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>15条</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>v4.0</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>46159</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="72" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>双模式选择：🅰 自主生成（全程无交互直接出docx）/ 🅱 人机协作（7步分步确认）。启动时提供选择。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>15条</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>v5.0</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>46159</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="72" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>二级矩阵规则修正：同项目课点分散在不同教学目标下（非集中）；二级/三级矩阵表头教学目标列写完整全文（不可简写）；思政融入覆盖全部课点（两大段叙述+精简表格）；教学目标加整体介绍段落；去掉课程进度表，附件直接一级→二级→三级矩阵；反向提示词21条。</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>21条</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>v5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>v6.0</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>46160</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>KSA编号全局唯一连续（K1-K96, S1-S64），禁止跨课点重复；教学目标严格引用大纲原文只字不差，去掉[]；空白模板课程基本信息精简为13项（去课程代码/性质/类别/考核/先修/后续），每项单独一行；启动时必问周次；二级矩阵设计前确认项目关系（并列/递进/包含）；三级矩阵每项末行"学习产出及测量标准（以教学目标为单位考核）"；1学时=1课点修正（项目二8→12课点，项目三14→10课点）；反向提示词26条。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>26条</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>v6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>46160</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>课程实施绑定句式：当涉及教学组织形式/团队学习方式/课堂互动方法时，自然嵌入"工作坊式的教学组织形式，集体主义的团队学习方式，教学相长的212学习方法。"三句连写不可拆分改动。212释义：2分钟小组展示、1分钟学生点评、2分钟教师点评。不强制放段首。反向提示词27条。新增Git Tag + GitHub Release发布规范。</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>27条</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v8.0</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>增强</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>新增学时跨目标核验规则（每课点按目标归属统计理论/实践，跨项目加总=二级矩阵学时统计行）；A值匹配教学目标列规则（目标1课点的A放C1列，目标2的放C2列）；三级矩阵汇总行（每项目末加"合 计"行，显示各目标学时分解+理论/实践）；新增格式规范_踩坑记录.md（13条格式硬约束+8次踩坑史）；新增教学大纲空白模板（含三段式预期学习产出）；核验清单升级（修改后自动验证KSA完整+学时加总+汇总行）；通识课5类专业分类（仅适用于面向多专业的通识必修课，专业课不分类）；教学大纲预期学习产出三段式（有形成果→任务要求→思政培养）；双文档联动说明（教学大纲+开课说明同步生成）。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>32条</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>v8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>v8.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>当前最新版本：v8.0 | 发布日期：2026-05-22 | 反向提示词：32条 | 空白模板：v8 | GitHub: https://github.com/mokch556-stack/ft-kecheng-kaifa</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
